--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665566</v>
+        <v>122665945</v>
       </c>
       <c r="B2" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596175</v>
+        <v>596236</v>
       </c>
       <c r="R2" t="n">
-        <v>7022813</v>
+        <v>7022742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665490</v>
+        <v>122665396</v>
       </c>
       <c r="B3" t="n">
-        <v>79738</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>7022892</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665396</v>
+        <v>122665566</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R4" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665945</v>
+        <v>122665547</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596236</v>
+        <v>596175</v>
       </c>
       <c r="R5" t="n">
-        <v>7022742</v>
+        <v>7022813</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665547</v>
+        <v>122665490</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R6" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1345,6 +1345,1585 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122674187</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596061</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022739</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122674692</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596198</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022609</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122675683</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596346</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7022636</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122681764</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79698</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596243</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7022587</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122674590</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596168</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7022670</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122674695</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596200</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7022601</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122674934</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596278</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7022583</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122674352</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>596121</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7022695</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122674516</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>596104</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7022690</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hela skogen garnlavsrik</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122674996</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>596279</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7022581</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122674874</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>596243</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7022587</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122675717</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79642</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>596377</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7022627</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122673905</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>596182</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7022708</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122675704</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>596356</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7022634</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122674306</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>596117</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7022707</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665945</v>
+        <v>122665396</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596236</v>
+        <v>596037</v>
       </c>
       <c r="R2" t="n">
-        <v>7022742</v>
+        <v>7022892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665396</v>
+        <v>122665474</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>7022892</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665566</v>
+        <v>122665490</v>
       </c>
       <c r="B4" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R4" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665547</v>
+        <v>122665566</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>79741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         <v>7022813</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665490</v>
+        <v>122665945</v>
       </c>
       <c r="B6" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596037</v>
+        <v>596236</v>
       </c>
       <c r="R6" t="n">
-        <v>7022892</v>
+        <v>7022742</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665474</v>
+        <v>122665547</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,37 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R7" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>122674187</v>
       </c>
       <c r="B8" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674692</v>
+        <v>122674695</v>
       </c>
       <c r="B9" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596198</v>
+        <v>596200</v>
       </c>
       <c r="R9" t="n">
-        <v>7022609</v>
+        <v>7022601</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1525,11 +1525,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122675683</v>
+        <v>122681764</v>
       </c>
       <c r="B10" t="n">
-        <v>79738</v>
+        <v>79701</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,41 +1563,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596346</v>
+        <v>596243</v>
       </c>
       <c r="R10" t="n">
-        <v>7022636</v>
+        <v>7022587</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,6 +1638,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1658,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122681764</v>
+        <v>122675683</v>
       </c>
       <c r="B11" t="n">
-        <v>79698</v>
+        <v>79741</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,44 +1669,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596243</v>
+        <v>596346</v>
       </c>
       <c r="R11" t="n">
-        <v>7022587</v>
+        <v>7022636</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,7 +1741,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1764,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122674590</v>
+        <v>122674692</v>
       </c>
       <c r="B12" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596168</v>
+        <v>596198</v>
       </c>
       <c r="R12" t="n">
-        <v>7022670</v>
+        <v>7022609</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1840,6 +1835,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674695</v>
+        <v>122674352</v>
       </c>
       <c r="B13" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,34 +1882,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596200</v>
+        <v>596121</v>
       </c>
       <c r="R13" t="n">
-        <v>7022601</v>
+        <v>7022695</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1942,6 +1947,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122674934</v>
+        <v>122674306</v>
       </c>
       <c r="B14" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,34 +1994,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596278</v>
+        <v>596117</v>
       </c>
       <c r="R14" t="n">
-        <v>7022583</v>
+        <v>7022707</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2044,6 +2059,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122674352</v>
+        <v>122674516</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,39 +2106,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596121</v>
+        <v>596104</v>
       </c>
       <c r="R15" t="n">
-        <v>7022695</v>
+        <v>7022690</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2155,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122674516</v>
+        <v>122675717</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>79645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,25 +2209,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596104</v>
+        <v>596377</v>
       </c>
       <c r="R16" t="n">
-        <v>7022690</v>
+        <v>7022627</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,11 +2273,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122674996</v>
+        <v>122674934</v>
       </c>
       <c r="B17" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596279</v>
+        <v>596278</v>
       </c>
       <c r="R17" t="n">
-        <v>7022581</v>
+        <v>7022583</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2391,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674874</v>
+        <v>122674590</v>
       </c>
       <c r="B18" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596243</v>
+        <v>596168</v>
       </c>
       <c r="R18" t="n">
-        <v>7022587</v>
+        <v>7022670</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2467,11 +2477,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122675717</v>
+        <v>122674996</v>
       </c>
       <c r="B19" t="n">
-        <v>79642</v>
+        <v>79741</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,25 +2515,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596377</v>
+        <v>596279</v>
       </c>
       <c r="R19" t="n">
-        <v>7022627</v>
+        <v>7022581</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2715,7 +2720,7 @@
         <v>122675704</v>
       </c>
       <c r="B21" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2814,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122674306</v>
+        <v>122674874</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,39 +2835,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596117</v>
+        <v>596243</v>
       </c>
       <c r="R22" t="n">
-        <v>7022707</v>
+        <v>7022587</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665396</v>
+        <v>122665945</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596037</v>
+        <v>596236</v>
       </c>
       <c r="R2" t="n">
-        <v>7022892</v>
+        <v>7022742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665474</v>
+        <v>122665490</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>79741</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>7022892</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665490</v>
+        <v>122665566</v>
       </c>
       <c r="B4" t="n">
         <v>79741</v>
@@ -935,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R4" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665566</v>
+        <v>122665396</v>
       </c>
       <c r="B5" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R5" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665945</v>
+        <v>122665474</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596236</v>
+        <v>596037</v>
       </c>
       <c r="R6" t="n">
-        <v>7022742</v>
+        <v>7022892</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122674187</v>
+        <v>122674934</v>
       </c>
       <c r="B8" t="n">
         <v>79741</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596061</v>
+        <v>596278</v>
       </c>
       <c r="R8" t="n">
-        <v>7022739</v>
+        <v>7022583</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674695</v>
+        <v>122674874</v>
       </c>
       <c r="B9" t="n">
         <v>79741</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596200</v>
+        <v>596243</v>
       </c>
       <c r="R9" t="n">
-        <v>7022601</v>
+        <v>7022587</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1525,6 +1525,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122681764</v>
+        <v>122674187</v>
       </c>
       <c r="B10" t="n">
-        <v>79701</v>
+        <v>79741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,44 +1568,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596243</v>
+        <v>596061</v>
       </c>
       <c r="R10" t="n">
-        <v>7022587</v>
+        <v>7022739</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1640,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1657,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122675683</v>
+        <v>122674996</v>
       </c>
       <c r="B11" t="n">
         <v>79741</v>
@@ -1697,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596346</v>
+        <v>596279</v>
       </c>
       <c r="R11" t="n">
-        <v>7022636</v>
+        <v>7022581</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1759,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122674692</v>
+        <v>122674516</v>
       </c>
       <c r="B12" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596198</v>
+        <v>596104</v>
       </c>
       <c r="R12" t="n">
-        <v>7022609</v>
+        <v>7022690</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1839,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122674306</v>
+        <v>122674695</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,39 +1995,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596117</v>
+        <v>596200</v>
       </c>
       <c r="R14" t="n">
-        <v>7022707</v>
+        <v>7022601</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2059,11 +2055,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122674516</v>
+        <v>122681764</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>79701</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,41 +2093,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596104</v>
+        <v>596243</v>
       </c>
       <c r="R15" t="n">
-        <v>7022690</v>
+        <v>7022587</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2168,17 +2162,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2197,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122675717</v>
+        <v>122674590</v>
       </c>
       <c r="B16" t="n">
-        <v>79645</v>
+        <v>79741</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,25 +2199,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596377</v>
+        <v>596168</v>
       </c>
       <c r="R16" t="n">
-        <v>7022627</v>
+        <v>7022670</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2299,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122674934</v>
+        <v>122675717</v>
       </c>
       <c r="B17" t="n">
-        <v>79741</v>
+        <v>79645</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,25 +2301,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2339,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596278</v>
+        <v>596377</v>
       </c>
       <c r="R17" t="n">
-        <v>7022583</v>
+        <v>7022627</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2401,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674590</v>
+        <v>122673905</v>
       </c>
       <c r="B18" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,34 +2407,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596168</v>
+        <v>596182</v>
       </c>
       <c r="R18" t="n">
-        <v>7022670</v>
+        <v>7022708</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2477,6 +2472,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,7 +2503,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674996</v>
+        <v>122675704</v>
       </c>
       <c r="B19" t="n">
         <v>79741</v>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596279</v>
+        <v>596356</v>
       </c>
       <c r="R19" t="n">
-        <v>7022581</v>
+        <v>7022634</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2605,7 +2605,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122673905</v>
+        <v>122674306</v>
       </c>
       <c r="B20" t="n">
         <v>57384</v>
@@ -2641,7 +2641,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596182</v>
+        <v>596117</v>
       </c>
       <c r="R20" t="n">
-        <v>7022708</v>
+        <v>7022707</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall på hygget</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122675704</v>
+        <v>122674692</v>
       </c>
       <c r="B21" t="n">
         <v>79741</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596356</v>
+        <v>596198</v>
       </c>
       <c r="R21" t="n">
-        <v>7022634</v>
+        <v>7022609</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2793,6 +2793,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2819,7 +2824,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122674874</v>
+        <v>122675683</v>
       </c>
       <c r="B22" t="n">
         <v>79741</v>
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596243</v>
+        <v>596346</v>
       </c>
       <c r="R22" t="n">
-        <v>7022587</v>
+        <v>7022636</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2895,11 +2900,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665490</v>
+        <v>122665945</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596037</v>
+        <v>596236</v>
       </c>
       <c r="R2" t="n">
-        <v>7022892</v>
+        <v>7022742</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>122665566</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665945</v>
+        <v>122665474</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596236</v>
+        <v>596037</v>
       </c>
       <c r="R4" t="n">
-        <v>7022742</v>
+        <v>7022892</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665396</v>
+        <v>122665547</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R5" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665547</v>
+        <v>122665490</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R6" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665474</v>
+        <v>122665396</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
         <v>7022892</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122674516</v>
+        <v>122675683</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596104</v>
+        <v>596346</v>
       </c>
       <c r="R8" t="n">
-        <v>7022690</v>
+        <v>7022636</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1423,11 +1423,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674306</v>
+        <v>122674187</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,39 +1465,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596117</v>
+        <v>596061</v>
       </c>
       <c r="R9" t="n">
-        <v>7022707</v>
+        <v>7022739</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1535,11 +1525,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122674187</v>
+        <v>122674516</v>
       </c>
       <c r="B10" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596061</v>
+        <v>596104</v>
       </c>
       <c r="R10" t="n">
-        <v>7022739</v>
+        <v>7022690</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122674695</v>
+        <v>122674934</v>
       </c>
       <c r="B11" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596200</v>
+        <v>596278</v>
       </c>
       <c r="R11" t="n">
-        <v>7022601</v>
+        <v>7022583</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122674590</v>
+        <v>122673905</v>
       </c>
       <c r="B12" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,34 +1776,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596168</v>
+        <v>596182</v>
       </c>
       <c r="R12" t="n">
-        <v>7022670</v>
+        <v>7022708</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1846,6 +1841,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674352</v>
+        <v>122674692</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,39 +1888,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596121</v>
+        <v>596198</v>
       </c>
       <c r="R13" t="n">
-        <v>7022695</v>
+        <v>7022609</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1957,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122675704</v>
+        <v>122674874</v>
       </c>
       <c r="B14" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596356</v>
+        <v>596243</v>
       </c>
       <c r="R14" t="n">
-        <v>7022634</v>
+        <v>7022587</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2060,6 +2055,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122675683</v>
+        <v>122674996</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596346</v>
+        <v>596279</v>
       </c>
       <c r="R15" t="n">
-        <v>7022636</v>
+        <v>7022581</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122674692</v>
+        <v>122675704</v>
       </c>
       <c r="B16" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596198</v>
+        <v>596356</v>
       </c>
       <c r="R16" t="n">
-        <v>7022609</v>
+        <v>7022634</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2264,11 +2264,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122681764</v>
+        <v>122675717</v>
       </c>
       <c r="B17" t="n">
-        <v>79803</v>
+        <v>79751</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,40 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596243</v>
+        <v>596377</v>
       </c>
       <c r="R17" t="n">
-        <v>7022587</v>
+        <v>7022627</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,7 +2374,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2401,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674934</v>
+        <v>122674306</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,34 +2408,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596278</v>
+        <v>596117</v>
       </c>
       <c r="R18" t="n">
-        <v>7022583</v>
+        <v>7022707</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2477,6 +2473,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674996</v>
+        <v>122681764</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>79807</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,41 +2516,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596279</v>
+        <v>596243</v>
       </c>
       <c r="R19" t="n">
-        <v>7022581</v>
+        <v>7022587</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,6 +2591,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2605,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122674874</v>
+        <v>122674695</v>
       </c>
       <c r="B20" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596243</v>
+        <v>596200</v>
       </c>
       <c r="R20" t="n">
-        <v>7022587</v>
+        <v>7022601</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2681,11 +2686,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,7 +2712,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122673905</v>
+        <v>122674352</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2748,7 +2748,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596182</v>
+        <v>596121</v>
       </c>
       <c r="R21" t="n">
-        <v>7022708</v>
+        <v>7022695</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall på hygget</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2824,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122675717</v>
+        <v>122674590</v>
       </c>
       <c r="B22" t="n">
-        <v>79747</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596377</v>
+        <v>596168</v>
       </c>
       <c r="R22" t="n">
-        <v>7022627</v>
+        <v>7022670</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2929,7 +2929,7 @@
         <v>122793714</v>
       </c>
       <c r="B23" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665547</v>
+        <v>122665396</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1047,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R5" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665490</v>
+        <v>122665547</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R6" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665396</v>
+        <v>122665490</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
         <v>7022892</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665945</v>
+        <v>122665490</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596236</v>
+        <v>596037</v>
       </c>
       <c r="R2" t="n">
-        <v>7022742</v>
+        <v>7022892</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665566</v>
+        <v>122665396</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R3" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665474</v>
+        <v>122665547</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R4" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665396</v>
+        <v>122665945</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596037</v>
+        <v>596236</v>
       </c>
       <c r="R5" t="n">
-        <v>7022892</v>
+        <v>7022742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665547</v>
+        <v>122665474</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R6" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665490</v>
+        <v>122665566</v>
       </c>
       <c r="B7" t="n">
         <v>79847</v>
@@ -1271,17 +1271,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R7" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122675683</v>
+        <v>122674590</v>
       </c>
       <c r="B8" t="n">
         <v>79847</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596346</v>
+        <v>596168</v>
       </c>
       <c r="R8" t="n">
-        <v>7022636</v>
+        <v>7022670</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674187</v>
+        <v>122674996</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596061</v>
+        <v>596279</v>
       </c>
       <c r="R9" t="n">
-        <v>7022739</v>
+        <v>7022581</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122674516</v>
+        <v>122674695</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596104</v>
+        <v>596200</v>
       </c>
       <c r="R10" t="n">
-        <v>7022690</v>
+        <v>7022601</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1627,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122674934</v>
+        <v>122675704</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1698,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596278</v>
+        <v>596356</v>
       </c>
       <c r="R11" t="n">
-        <v>7022583</v>
+        <v>7022634</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1760,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122673905</v>
+        <v>122674934</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,39 +1771,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596182</v>
+        <v>596278</v>
       </c>
       <c r="R12" t="n">
-        <v>7022708</v>
+        <v>7022583</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1841,11 +1831,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,7 +1964,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122674874</v>
+        <v>122675683</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2019,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596243</v>
+        <v>596346</v>
       </c>
       <c r="R14" t="n">
-        <v>7022587</v>
+        <v>7022636</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2055,11 +2040,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122674996</v>
+        <v>122674352</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,34 +2082,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596279</v>
+        <v>596121</v>
       </c>
       <c r="R15" t="n">
-        <v>7022581</v>
+        <v>7022695</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2162,6 +2147,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122675704</v>
+        <v>122673905</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,34 +2194,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596356</v>
+        <v>596182</v>
       </c>
       <c r="R16" t="n">
-        <v>7022634</v>
+        <v>7022708</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2264,6 +2259,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122675717</v>
+        <v>122674187</v>
       </c>
       <c r="B17" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,25 +2302,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596377</v>
+        <v>596061</v>
       </c>
       <c r="R17" t="n">
-        <v>7022627</v>
+        <v>7022739</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674306</v>
+        <v>122681764</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,46 +2404,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596117</v>
+        <v>596243</v>
       </c>
       <c r="R18" t="n">
-        <v>7022707</v>
+        <v>7022587</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,17 +2473,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2504,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122681764</v>
+        <v>122674516</v>
       </c>
       <c r="B19" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,44 +2510,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596243</v>
+        <v>596104</v>
       </c>
       <c r="R19" t="n">
-        <v>7022587</v>
+        <v>7022690</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2585,13 +2576,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hela skogen garnlavsrik</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2610,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122674695</v>
+        <v>122675717</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,25 +2617,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596200</v>
+        <v>596377</v>
       </c>
       <c r="R20" t="n">
-        <v>7022601</v>
+        <v>7022627</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2712,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122674352</v>
+        <v>122674874</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,39 +2723,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596121</v>
+        <v>596243</v>
       </c>
       <c r="R21" t="n">
-        <v>7022695</v>
+        <v>7022587</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2797,7 +2787,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2824,10 +2814,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122674590</v>
+        <v>122674306</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,34 +2830,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596168</v>
+        <v>596117</v>
       </c>
       <c r="R22" t="n">
-        <v>7022670</v>
+        <v>7022707</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2900,6 +2895,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665490</v>
+        <v>122665474</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>7022892</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665396</v>
+        <v>122665945</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596037</v>
+        <v>596236</v>
       </c>
       <c r="R3" t="n">
-        <v>7022892</v>
+        <v>7022742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665547</v>
+        <v>122665490</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R4" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665945</v>
+        <v>122665547</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596236</v>
+        <v>596175</v>
       </c>
       <c r="R5" t="n">
-        <v>7022742</v>
+        <v>7022813</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665474</v>
+        <v>122665566</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,37 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R6" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665566</v>
+        <v>122665396</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R7" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122674590</v>
+        <v>122674516</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596168</v>
+        <v>596104</v>
       </c>
       <c r="R8" t="n">
-        <v>7022670</v>
+        <v>7022690</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1423,6 +1423,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,7 +1556,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122674695</v>
+        <v>122675704</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1591,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596200</v>
+        <v>596356</v>
       </c>
       <c r="R10" t="n">
-        <v>7022601</v>
+        <v>7022634</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1653,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122675704</v>
+        <v>122674590</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596356</v>
+        <v>596168</v>
       </c>
       <c r="R11" t="n">
-        <v>7022634</v>
+        <v>7022670</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1755,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122674934</v>
+        <v>122674352</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,34 +1776,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596278</v>
+        <v>596121</v>
       </c>
       <c r="R12" t="n">
-        <v>7022583</v>
+        <v>7022695</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1831,6 +1841,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674692</v>
+        <v>122674187</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1897,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596198</v>
+        <v>596061</v>
       </c>
       <c r="R13" t="n">
-        <v>7022609</v>
+        <v>7022739</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1933,11 +1948,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122674352</v>
+        <v>122673905</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2102,7 +2112,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2111,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596121</v>
+        <v>596182</v>
       </c>
       <c r="R15" t="n">
-        <v>7022695</v>
+        <v>7022708</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2151,7 +2161,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122673905</v>
+        <v>122674874</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,39 +2204,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596182</v>
+        <v>596243</v>
       </c>
       <c r="R16" t="n">
-        <v>7022708</v>
+        <v>7022587</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2263,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall på hygget</t>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122674187</v>
+        <v>122681764</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,41 +2307,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596061</v>
+        <v>596243</v>
       </c>
       <c r="R17" t="n">
-        <v>7022739</v>
+        <v>7022587</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2374,6 +2382,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2392,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122681764</v>
+        <v>122674934</v>
       </c>
       <c r="B18" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,44 +2413,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596243</v>
+        <v>596278</v>
       </c>
       <c r="R18" t="n">
-        <v>7022587</v>
+        <v>7022583</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2479,7 +2485,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2498,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674516</v>
+        <v>122674692</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,21 +2519,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596104</v>
+        <v>596198</v>
       </c>
       <c r="R19" t="n">
-        <v>7022690</v>
+        <v>7022609</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2578,7 +2583,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hela skogen garnlavsrik</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122675717</v>
+        <v>122674695</v>
       </c>
       <c r="B20" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,25 +2622,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596377</v>
+        <v>596200</v>
       </c>
       <c r="R20" t="n">
-        <v>7022627</v>
+        <v>7022601</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2707,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122674874</v>
+        <v>122674306</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,34 +2728,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596243</v>
+        <v>596117</v>
       </c>
       <c r="R21" t="n">
-        <v>7022587</v>
+        <v>7022707</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2787,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122674306</v>
+        <v>122675717</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,43 +2836,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596117</v>
+        <v>596377</v>
       </c>
       <c r="R22" t="n">
-        <v>7022707</v>
+        <v>7022627</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2895,11 +2900,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122674874</v>
+        <v>122681764</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,31 +2200,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2234,7 +2237,7 @@
         <v>7022587</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,17 +2269,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2295,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122681764</v>
+        <v>122674874</v>
       </c>
       <c r="B17" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,34 +2306,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2344,7 +2340,7 @@
         <v>7022587</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2376,13 +2372,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122675683</v>
+        <v>122673905</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,34 +1990,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596346</v>
+        <v>596182</v>
       </c>
       <c r="R14" t="n">
-        <v>7022636</v>
+        <v>7022708</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,6 +2055,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122673905</v>
+        <v>122675683</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,39 +2102,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596182</v>
+        <v>596346</v>
       </c>
       <c r="R15" t="n">
-        <v>7022708</v>
+        <v>7022636</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2157,11 +2162,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122673905</v>
+        <v>122675683</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,39 +1990,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596182</v>
+        <v>596346</v>
       </c>
       <c r="R14" t="n">
-        <v>7022708</v>
+        <v>7022636</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2055,11 +2050,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122675683</v>
+        <v>122673905</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,34 +2092,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596346</v>
+        <v>596182</v>
       </c>
       <c r="R15" t="n">
-        <v>7022636</v>
+        <v>7022708</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2162,6 +2157,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665474</v>
+        <v>122665396</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>7022892</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665945</v>
+        <v>122665490</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596236</v>
+        <v>596037</v>
       </c>
       <c r="R3" t="n">
-        <v>7022742</v>
+        <v>7022892</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665490</v>
+        <v>122665547</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R4" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665547</v>
+        <v>122665566</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         <v>7022813</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665566</v>
+        <v>122665945</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596175</v>
+        <v>596236</v>
       </c>
       <c r="R6" t="n">
-        <v>7022813</v>
+        <v>7022742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665396</v>
+        <v>122665474</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
         <v>7022892</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122674516</v>
+        <v>122681764</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,41 +1359,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596104</v>
+        <v>596243</v>
       </c>
       <c r="R8" t="n">
-        <v>7022690</v>
+        <v>7022587</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,17 +1428,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674996</v>
+        <v>122675717</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596279</v>
+        <v>596377</v>
       </c>
       <c r="R9" t="n">
-        <v>7022581</v>
+        <v>7022627</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1556,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122675704</v>
+        <v>122675683</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1596,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596356</v>
+        <v>596346</v>
       </c>
       <c r="R10" t="n">
-        <v>7022634</v>
+        <v>7022636</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1658,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122674590</v>
+        <v>122674306</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,34 +1673,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596168</v>
+        <v>596117</v>
       </c>
       <c r="R11" t="n">
-        <v>7022670</v>
+        <v>7022707</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1734,6 +1738,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122674352</v>
+        <v>122674692</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,39 +1785,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596121</v>
+        <v>596198</v>
       </c>
       <c r="R12" t="n">
-        <v>7022695</v>
+        <v>7022609</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674187</v>
+        <v>122674352</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,34 +1892,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596061</v>
+        <v>596121</v>
       </c>
       <c r="R13" t="n">
-        <v>7022739</v>
+        <v>7022695</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1948,6 +1957,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1988,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122675683</v>
+        <v>122674874</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2014,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596346</v>
+        <v>596243</v>
       </c>
       <c r="R14" t="n">
-        <v>7022636</v>
+        <v>7022587</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,6 +2064,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122673905</v>
+        <v>122674695</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,39 +2111,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596182</v>
+        <v>596200</v>
       </c>
       <c r="R15" t="n">
-        <v>7022708</v>
+        <v>7022601</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2157,11 +2171,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122681764</v>
+        <v>122674187</v>
       </c>
       <c r="B16" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,44 +2209,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596243</v>
+        <v>596061</v>
       </c>
       <c r="R16" t="n">
-        <v>7022587</v>
+        <v>7022739</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,7 +2281,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2294,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122674874</v>
+        <v>122674996</v>
       </c>
       <c r="B17" t="n">
         <v>79847</v>
@@ -2334,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596243</v>
+        <v>596279</v>
       </c>
       <c r="R17" t="n">
-        <v>7022587</v>
+        <v>7022581</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2370,11 +2375,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674934</v>
+        <v>122675704</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596278</v>
+        <v>596356</v>
       </c>
       <c r="R18" t="n">
-        <v>7022583</v>
+        <v>7022634</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674692</v>
+        <v>122674590</v>
       </c>
       <c r="B19" t="n">
         <v>79847</v>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596198</v>
+        <v>596168</v>
       </c>
       <c r="R19" t="n">
-        <v>7022609</v>
+        <v>7022670</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2579,11 +2579,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122674695</v>
+        <v>122673905</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,34 +2621,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596200</v>
+        <v>596182</v>
       </c>
       <c r="R20" t="n">
-        <v>7022601</v>
+        <v>7022708</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2686,6 +2686,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122674306</v>
+        <v>122674516</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,39 +2733,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596117</v>
+        <v>596104</v>
       </c>
       <c r="R21" t="n">
-        <v>7022707</v>
+        <v>7022690</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2824,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122675717</v>
+        <v>122674934</v>
       </c>
       <c r="B22" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596377</v>
+        <v>596278</v>
       </c>
       <c r="R22" t="n">
-        <v>7022627</v>
+        <v>7022583</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122675683</v>
+        <v>122674306</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,34 +1571,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596346</v>
+        <v>596117</v>
       </c>
       <c r="R10" t="n">
-        <v>7022636</v>
+        <v>7022707</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1631,6 +1636,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122674306</v>
+        <v>122675683</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,39 +1683,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596117</v>
+        <v>596346</v>
       </c>
       <c r="R11" t="n">
-        <v>7022707</v>
+        <v>7022636</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1738,11 +1743,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122674306</v>
+        <v>122675683</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,39 +1571,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596117</v>
+        <v>596346</v>
       </c>
       <c r="R10" t="n">
-        <v>7022707</v>
+        <v>7022636</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1636,11 +1631,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122675683</v>
+        <v>122674306</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,34 +1673,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596346</v>
+        <v>596117</v>
       </c>
       <c r="R11" t="n">
-        <v>7022636</v>
+        <v>7022707</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1743,6 +1738,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665396</v>
+        <v>122665474</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>7022892</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665566</v>
+        <v>122665945</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596175</v>
+        <v>596236</v>
       </c>
       <c r="R5" t="n">
-        <v>7022813</v>
+        <v>7022742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665945</v>
+        <v>122665566</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596236</v>
+        <v>596175</v>
       </c>
       <c r="R6" t="n">
-        <v>7022742</v>
+        <v>7022813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665474</v>
+        <v>122665396</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
         <v>7022892</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122681764</v>
+        <v>122673905</v>
       </c>
       <c r="B8" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,44 +1359,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596243</v>
+        <v>596182</v>
       </c>
       <c r="R8" t="n">
-        <v>7022587</v>
+        <v>7022708</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,13 +1430,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1453,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122675717</v>
+        <v>122674874</v>
       </c>
       <c r="B9" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596377</v>
+        <v>596243</v>
       </c>
       <c r="R9" t="n">
-        <v>7022627</v>
+        <v>7022587</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1529,6 +1535,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122675683</v>
+        <v>122674306</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,34 +1582,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596346</v>
+        <v>596117</v>
       </c>
       <c r="R10" t="n">
-        <v>7022636</v>
+        <v>7022707</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1631,6 +1647,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122674306</v>
+        <v>122674996</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,39 +1694,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596117</v>
+        <v>596279</v>
       </c>
       <c r="R11" t="n">
-        <v>7022707</v>
+        <v>7022581</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1738,11 +1754,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122674692</v>
+        <v>122675683</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1809,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596198</v>
+        <v>596346</v>
       </c>
       <c r="R12" t="n">
-        <v>7022609</v>
+        <v>7022636</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1845,11 +1856,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674352</v>
+        <v>122674695</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,39 +1898,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596121</v>
+        <v>596200</v>
       </c>
       <c r="R13" t="n">
-        <v>7022695</v>
+        <v>7022601</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1957,11 +1958,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122674874</v>
+        <v>122674187</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2028,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596243</v>
+        <v>596061</v>
       </c>
       <c r="R14" t="n">
-        <v>7022587</v>
+        <v>7022739</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2064,11 +2060,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122674695</v>
+        <v>122674352</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,34 +2102,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596200</v>
+        <v>596121</v>
       </c>
       <c r="R15" t="n">
-        <v>7022601</v>
+        <v>7022695</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2171,6 +2167,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122674187</v>
+        <v>122681764</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,41 +2210,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596061</v>
+        <v>596243</v>
       </c>
       <c r="R16" t="n">
-        <v>7022739</v>
+        <v>7022587</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,6 +2285,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2299,7 +2304,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122674996</v>
+        <v>122674934</v>
       </c>
       <c r="B17" t="n">
         <v>79847</v>
@@ -2339,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596279</v>
+        <v>596278</v>
       </c>
       <c r="R17" t="n">
-        <v>7022581</v>
+        <v>7022583</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2401,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122675704</v>
+        <v>122675717</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2413,25 +2418,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596356</v>
+        <v>596377</v>
       </c>
       <c r="R18" t="n">
-        <v>7022634</v>
+        <v>7022627</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2503,7 +2508,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674590</v>
+        <v>122674692</v>
       </c>
       <c r="B19" t="n">
         <v>79847</v>
@@ -2543,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596168</v>
+        <v>596198</v>
       </c>
       <c r="R19" t="n">
-        <v>7022670</v>
+        <v>7022609</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2579,6 +2584,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122673905</v>
+        <v>122674590</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,39 +2631,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596182</v>
+        <v>596168</v>
       </c>
       <c r="R20" t="n">
-        <v>7022708</v>
+        <v>7022670</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2686,11 +2691,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122674516</v>
+        <v>122675704</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596104</v>
+        <v>596356</v>
       </c>
       <c r="R21" t="n">
-        <v>7022690</v>
+        <v>7022634</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2793,11 +2793,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2824,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122674934</v>
+        <v>122674516</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,21 +2835,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596278</v>
+        <v>596104</v>
       </c>
       <c r="R22" t="n">
-        <v>7022583</v>
+        <v>7022690</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2900,6 +2895,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,7 +2929,7 @@
         <v>122793714</v>
       </c>
       <c r="B23" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665474</v>
+        <v>122665945</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596037</v>
+        <v>596236</v>
       </c>
       <c r="R2" t="n">
-        <v>7022892</v>
+        <v>7022742</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665490</v>
+        <v>122665474</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>7022892</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665547</v>
+        <v>122665566</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,7 +945,7 @@
         <v>7022813</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665945</v>
+        <v>122665396</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596236</v>
+        <v>596037</v>
       </c>
       <c r="R5" t="n">
-        <v>7022742</v>
+        <v>7022892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665566</v>
+        <v>122665547</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
         <v>7022813</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665396</v>
+        <v>122665490</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
         <v>7022892</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122673905</v>
+        <v>122674516</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,39 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596182</v>
+        <v>596104</v>
       </c>
       <c r="R8" t="n">
-        <v>7022708</v>
+        <v>7022690</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall på hygget</t>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674874</v>
+        <v>122674352</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,34 +1470,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596243</v>
+        <v>596121</v>
       </c>
       <c r="R9" t="n">
-        <v>7022587</v>
+        <v>7022695</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122674306</v>
+        <v>122674692</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,39 +1582,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596117</v>
+        <v>596198</v>
       </c>
       <c r="R10" t="n">
-        <v>7022707</v>
+        <v>7022609</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack, tall</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122674996</v>
+        <v>122675717</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,25 +1685,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596279</v>
+        <v>596377</v>
       </c>
       <c r="R11" t="n">
-        <v>7022581</v>
+        <v>7022627</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1780,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122675683</v>
+        <v>122673905</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,34 +1791,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596346</v>
+        <v>596182</v>
       </c>
       <c r="R12" t="n">
-        <v>7022636</v>
+        <v>7022708</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,6 +1856,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1887,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674695</v>
+        <v>122674996</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1922,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596200</v>
+        <v>596279</v>
       </c>
       <c r="R13" t="n">
-        <v>7022601</v>
+        <v>7022581</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1984,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122674187</v>
+        <v>122675683</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2024,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596061</v>
+        <v>596346</v>
       </c>
       <c r="R14" t="n">
-        <v>7022739</v>
+        <v>7022636</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2086,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122674352</v>
+        <v>122681764</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,46 +2103,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596121</v>
+        <v>596243</v>
       </c>
       <c r="R15" t="n">
-        <v>7022695</v>
+        <v>7022587</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,17 +2172,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2198,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122681764</v>
+        <v>122674590</v>
       </c>
       <c r="B16" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,44 +2209,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596243</v>
+        <v>596168</v>
       </c>
       <c r="R16" t="n">
-        <v>7022587</v>
+        <v>7022670</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2285,7 +2281,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122674934</v>
+        <v>122674306</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,34 +2315,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596278</v>
+        <v>596117</v>
       </c>
       <c r="R17" t="n">
-        <v>7022583</v>
+        <v>7022707</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2380,6 +2380,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122675717</v>
+        <v>122674934</v>
       </c>
       <c r="B18" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,25 +2423,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2446,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596377</v>
+        <v>596278</v>
       </c>
       <c r="R18" t="n">
-        <v>7022627</v>
+        <v>7022583</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2508,7 +2513,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674692</v>
+        <v>122674695</v>
       </c>
       <c r="B19" t="n">
         <v>79847</v>
@@ -2548,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596198</v>
+        <v>596200</v>
       </c>
       <c r="R19" t="n">
-        <v>7022609</v>
+        <v>7022601</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2584,11 +2589,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122674590</v>
+        <v>122674874</v>
       </c>
       <c r="B20" t="n">
         <v>79847</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596168</v>
+        <v>596243</v>
       </c>
       <c r="R20" t="n">
-        <v>7022670</v>
+        <v>7022587</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2691,6 +2691,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122675704</v>
+        <v>122674187</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2757,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596356</v>
+        <v>596061</v>
       </c>
       <c r="R21" t="n">
-        <v>7022634</v>
+        <v>7022739</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2819,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122674516</v>
+        <v>122675704</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,21 +2840,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596104</v>
+        <v>596356</v>
       </c>
       <c r="R22" t="n">
-        <v>7022690</v>
+        <v>7022634</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2895,11 +2900,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665945</v>
+        <v>122665474</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596236</v>
+        <v>596037</v>
       </c>
       <c r="R2" t="n">
-        <v>7022742</v>
+        <v>7022892</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665474</v>
+        <v>122665547</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R3" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665396</v>
+        <v>122665490</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         <v>7022892</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122665547</v>
+        <v>122665945</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596175</v>
+        <v>596236</v>
       </c>
       <c r="R6" t="n">
-        <v>7022813</v>
+        <v>7022742</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122665490</v>
+        <v>122665396</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
         <v>7022892</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122674516</v>
+        <v>122674306</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596104</v>
+        <v>596117</v>
       </c>
       <c r="R8" t="n">
-        <v>7022690</v>
+        <v>7022707</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hela skogen garnlavsrik</t>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122674692</v>
+        <v>122675683</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1606,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596198</v>
+        <v>596346</v>
       </c>
       <c r="R10" t="n">
-        <v>7022609</v>
+        <v>7022636</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1642,11 +1647,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122673905</v>
+        <v>122674695</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,39 +1791,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596182</v>
+        <v>596200</v>
       </c>
       <c r="R12" t="n">
-        <v>7022708</v>
+        <v>7022601</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,11 +1851,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674996</v>
+        <v>122674934</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1927,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596279</v>
+        <v>596278</v>
       </c>
       <c r="R13" t="n">
-        <v>7022581</v>
+        <v>7022583</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1989,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122675683</v>
+        <v>122674516</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596346</v>
+        <v>596104</v>
       </c>
       <c r="R14" t="n">
-        <v>7022636</v>
+        <v>7022690</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2065,6 +2055,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122681764</v>
+        <v>122674692</v>
       </c>
       <c r="B15" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,44 +2098,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596243</v>
+        <v>596198</v>
       </c>
       <c r="R15" t="n">
-        <v>7022587</v>
+        <v>7022609</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2172,13 +2164,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2197,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122674590</v>
+        <v>122674996</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2237,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596168</v>
+        <v>596279</v>
       </c>
       <c r="R16" t="n">
-        <v>7022670</v>
+        <v>7022581</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2299,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122674306</v>
+        <v>122675704</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,39 +2311,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596117</v>
+        <v>596356</v>
       </c>
       <c r="R17" t="n">
-        <v>7022707</v>
+        <v>7022634</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2380,11 +2371,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674934</v>
+        <v>122674874</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2451,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596278</v>
+        <v>596243</v>
       </c>
       <c r="R18" t="n">
-        <v>7022583</v>
+        <v>7022587</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2487,6 +2473,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674695</v>
+        <v>122681764</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,41 +2516,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596200</v>
+        <v>596243</v>
       </c>
       <c r="R19" t="n">
-        <v>7022601</v>
+        <v>7022587</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,6 +2591,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2615,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122674874</v>
+        <v>122673905</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,34 +2626,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596243</v>
+        <v>596182</v>
       </c>
       <c r="R20" t="n">
-        <v>7022587</v>
+        <v>7022708</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,7 +2824,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122675704</v>
+        <v>122674590</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596356</v>
+        <v>596168</v>
       </c>
       <c r="R22" t="n">
-        <v>7022634</v>
+        <v>7022670</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122665474</v>
+        <v>122665547</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R2" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122665547</v>
+        <v>122665474</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R3" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122665566</v>
+        <v>122665490</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -935,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596175</v>
+        <v>596037</v>
       </c>
       <c r="R4" t="n">
-        <v>7022813</v>
+        <v>7022892</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122665490</v>
+        <v>122665566</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1047,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräsbergsbodarna, Gräsbergsbodarna, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596037</v>
+        <v>596175</v>
       </c>
       <c r="R5" t="n">
-        <v>7022892</v>
+        <v>7022813</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122674306</v>
+        <v>122675717</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,43 +1359,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596117</v>
+        <v>596377</v>
       </c>
       <c r="R8" t="n">
-        <v>7022707</v>
+        <v>7022627</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1428,11 +1423,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674352</v>
+        <v>122674306</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1504,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596121</v>
+        <v>596117</v>
       </c>
       <c r="R9" t="n">
-        <v>7022695</v>
+        <v>7022707</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122675683</v>
+        <v>122674516</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596346</v>
+        <v>596104</v>
       </c>
       <c r="R10" t="n">
-        <v>7022636</v>
+        <v>7022690</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1647,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122675717</v>
+        <v>122681764</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>79807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,37 +1684,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596377</v>
+        <v>596243</v>
       </c>
       <c r="R11" t="n">
-        <v>7022627</v>
+        <v>7022587</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,6 +1755,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1774,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122674695</v>
+        <v>122674934</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1815,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596200</v>
+        <v>596278</v>
       </c>
       <c r="R12" t="n">
-        <v>7022601</v>
+        <v>7022583</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1877,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122674934</v>
+        <v>122673905</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,34 +1892,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596278</v>
+        <v>596182</v>
       </c>
       <c r="R13" t="n">
-        <v>7022583</v>
+        <v>7022708</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1953,6 +1957,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall på hygget</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122674516</v>
+        <v>122675704</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +2004,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596104</v>
+        <v>596356</v>
       </c>
       <c r="R14" t="n">
-        <v>7022690</v>
+        <v>7022634</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2055,11 +2064,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hela skogen garnlavsrik</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2090,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122674692</v>
+        <v>122674874</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2126,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596198</v>
+        <v>596243</v>
       </c>
       <c r="R15" t="n">
-        <v>7022609</v>
+        <v>7022587</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2166,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122674996</v>
+        <v>122674187</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2233,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596279</v>
+        <v>596061</v>
       </c>
       <c r="R16" t="n">
-        <v>7022581</v>
+        <v>7022739</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2295,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122675704</v>
+        <v>122674695</v>
       </c>
       <c r="B17" t="n">
         <v>79847</v>
@@ -2335,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596356</v>
+        <v>596200</v>
       </c>
       <c r="R17" t="n">
-        <v>7022634</v>
+        <v>7022601</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2397,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674874</v>
+        <v>122674590</v>
       </c>
       <c r="B18" t="n">
         <v>79847</v>
@@ -2437,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596243</v>
+        <v>596168</v>
       </c>
       <c r="R18" t="n">
-        <v>7022587</v>
+        <v>7022670</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2473,11 +2477,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Asp, högstubbe 72 cm diameter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122681764</v>
+        <v>122674352</v>
       </c>
       <c r="B19" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,44 +2515,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tängsta-Stormyran, Ång</t>
+          <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596243</v>
+        <v>596121</v>
       </c>
       <c r="R19" t="n">
-        <v>7022587</v>
+        <v>7022695</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2585,13 +2586,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2610,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122673905</v>
+        <v>122674692</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,39 +2631,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596182</v>
+        <v>596198</v>
       </c>
       <c r="R20" t="n">
-        <v>7022708</v>
+        <v>7022609</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall på hygget</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122674187</v>
+        <v>122674996</v>
       </c>
       <c r="B21" t="n">
         <v>79847</v>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596061</v>
+        <v>596279</v>
       </c>
       <c r="R21" t="n">
-        <v>7022739</v>
+        <v>7022581</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122674590</v>
+        <v>122675683</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596168</v>
+        <v>596346</v>
       </c>
       <c r="R22" t="n">
-        <v>7022670</v>
+        <v>7022636</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122675717</v>
+        <v>122674306</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,38 +1359,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596377</v>
+        <v>596117</v>
       </c>
       <c r="R8" t="n">
-        <v>7022627</v>
+        <v>7022707</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1423,6 +1428,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122674306</v>
+        <v>122675717</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,43 +1471,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596117</v>
+        <v>596377</v>
       </c>
       <c r="R9" t="n">
-        <v>7022707</v>
+        <v>7022627</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1530,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2401,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122674590</v>
+        <v>122674352</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,34 +2417,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596168</v>
+        <v>596121</v>
       </c>
       <c r="R18" t="n">
-        <v>7022670</v>
+        <v>7022695</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2477,6 +2482,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122674352</v>
+        <v>122674590</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,39 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tängsta-Stormyran, Tängsta-Stormyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596121</v>
+        <v>596168</v>
       </c>
       <c r="R19" t="n">
-        <v>7022695</v>
+        <v>7022670</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2584,11 +2589,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -2929,7 +2929,7 @@
         <v>122793714</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -2929,7 +2929,7 @@
         <v>122793714</v>
       </c>
       <c r="B23" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 60956-2024 artfynd.xlsx
+++ b/artfynd/A 60956-2024 artfynd.xlsx
@@ -2929,7 +2929,7 @@
         <v>122793714</v>
       </c>
       <c r="B23" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
